--- a/public/crawlability-bespirit-september-2026.xlsx
+++ b/public/crawlability-bespirit-september-2026.xlsx
@@ -11,10 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="404 ושגיאות" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="לולאות, שרשראות, 302" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="קישורים להפניות 301" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="לבדיקה" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="robots, sitemap, אינדוקס" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="תת-דומיינים" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מקורות" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="robots, sitemap, אינדוקס" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="תת-דומיינים" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מקורות" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -484,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -618,12 +617,27 @@
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>קישורים פנימיים ללא לוכסן סופי: 3 כתובות (הבולטת: https://bespirit.co.il/nlp-treatment-in…ctive-situations/ ‎, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>לבדיקה</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>לאשר ש-4 העמודים המוגדרים noindex אכן אמורים להישאר מחוץ לאינדקס.</t>
         </is>
@@ -756,7 +770,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור; להגדיר הפניית 301 ליעד המצוין. קישור 'מדיניות הפרטיות' בפוטר בכל עמודי האתר מצביע על מזהה עמוד שאינו קיים; עמוד מדיניות הפרטיות קיים בכתובת היעד. לעדכן את הקישור בתבנית הפוטר.</t>
+          <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (אומת כעמוד תקין ב-27.09.2026). קישור 'מדיניות הפרטיות' בפוטר בכל עמודי האתר מצביע על מזהה עמוד שאינו קיים; עמוד מדיניות הפרטיות קיים בכתובת היעד. לעדכן את הקישור בתבנית הפוטר.</t>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr">
@@ -813,7 +827,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור; להגדיר הפניית 301 ליעד המצוין. העמוד שהוסר נשא את הכותרת 'לימודי פסיכותרפיה גופנית' (ארכיון 2020); תכנית לימודי פסיכותרפיה גופנית קיימת כיום בכתובת היעד.</t>
+          <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (אומת כעמוד תקין ב-27.09.2026). העמוד שהוסר נשא את הכותרת 'לימודי פסיכותרפיה גופנית' (ארכיון 2020); תכנית לימודי פסיכותרפיה גופנית קיימת כיום בכתובת היעד.</t>
         </is>
       </c>
       <c r="J3" s="7" t="inlineStr">
@@ -862,7 +876,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור; להגדיר הפניית 301 ליעד המצוין. סדנת מיינדפולנס אונליין שהסתיימה (ארכיון פברואר 2026); קורס המיינדפולנס קיים בכתובת היעד. לאישור.</t>
+          <t>לתקן או להסיר את הקישור בעמודי המקור. יעד מוצע להפניית 301 (אומת כעמוד תקין), לאישור הלקוח. סדנת מיינדפולנס אונליין שהסתיימה (ארכיון פברואר 2026); קורס המיינדפולנס קיים בכתובת היעד. לאישור.</t>
         </is>
       </c>
       <c r="J4" s="7" t="inlineStr">
@@ -910,7 +924,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור. לא נמצא עמוד חלופי מובהק; אם קיים, להגדיר הפניית 301 (יעד לאישור). קישור 'לדף המנחה' לעמוד מנחה שנמחק. להסיר את הקישור או לשחזר את עמוד המנחה.</t>
+          <t>קישור 'לדף המנחה' לעמוד מנחה שנמחק. להסיר את הקישור או לשחזר את עמוד המנחה.</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
@@ -954,7 +968,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור. לא נמצא עמוד חלופי מובהק; אם קיים, להגדיר הפניית 301 (יעד לאישור). קישור 'לדף המנחה' לעמוד מנחה שנמחק. להסיר את הקישור או לשחזר את עמוד המנחה.</t>
+          <t>קישור 'לדף המנחה' לעמוד מנחה שנמחק. להסיר את הקישור או לשחזר את עמוד המנחה.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
@@ -997,7 +1011,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור; להגדיר הפניית 301 ליעד המצוין. העמוד שהוסר נשא את הכותרת 'מטפלים בהפרעות קשב וריכוז (ADHD)' (ארכיון דצמבר 2024); קורס אימון ADHD קיים בכתובת היעד. לאישור.</t>
+          <t>לתקן או להסיר את הקישור בעמודי המקור. יעד מוצע להפניית 301 (אומת כעמוד תקין), לאישור הלקוח. העמוד שהוסר נשא את הכותרת 'מטפלים בהפרעות קשב וריכוז (ADHD)' (ארכיון דצמבר 2024); קורס אימון ADHD קיים בכתובת היעד. לאישור.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
@@ -1040,7 +1054,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור. לא נמצא עמוד חלופי מובהק; אם קיים, להגדיר הפניית 301 (יעד לאישור). מזהה קורס שנמחק. להסיר את הקישור.</t>
+          <t>מזהה קורס שנמחק. להסיר את הקישור.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
@@ -1083,7 +1097,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור; להגדיר הפניית 301 ליעד המצוין. תכנית 'לימודי סביבה וקיימות' שהוסרה; אין תכנית מקבילה פעילה. יעד משוער: קטגוריית סביבה וקיימות. לאישור.</t>
+          <t>לתקן או להסיר את הקישור בעמודי המקור. יעד מוצע להפניית 301 (אומת כעמוד תקין), לאישור הלקוח. תכנית 'לימודי סביבה וקיימות' שהוסרה; אין תכנית מקבילה פעילה. יעד משוער: קטגוריית סביבה וקיימות. לאישור.</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">
@@ -1523,7 +1537,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור.</t>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה; המקור עשוי להיות תגית canonical/hreflang, קובץ סטטי או קישור חיצוני. לאתר את המקור ולתקן; אין צורך בהפניה.</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
@@ -1566,7 +1580,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור; להגדיר הפניית 301 ליעד המצוין. תכנית 'יועצי סביבה וקיימות' שהוסרה (ארכיון יולי 2024); אין תכנית מקבילה פעילה. יעד משוער: קטגוריית סביבה וקיימות. לאישור.</t>
+          <t>לתקן או להסיר את הקישור בעמודי המקור. יעד מוצע להפניית 301 (אומת כעמוד תקין), לאישור הלקוח. תכנית 'יועצי סביבה וקיימות' שהוסרה (ארכיון יולי 2024); אין תכנית מקבילה פעילה. יעד משוער: קטגוריית סביבה וקיימות. לאישור.</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr">
@@ -1974,7 +1988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K289"/>
+  <dimension ref="A1:K292"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -17653,7 +17667,7 @@
       </c>
       <c r="I289" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
         </is>
       </c>
       <c r="J289" s="7" t="inlineStr">
@@ -17662,6 +17676,159 @@
         </is>
       </c>
       <c r="K289" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/nlp-treatment-in…ctive-situations/ ‎</t>
+        </is>
+      </c>
+      <c r="B290" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C290" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D290" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/</t>
+        </is>
+      </c>
+      <c r="E290" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F290" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G290" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/nlp-drugs-and-addictions/</t>
+        </is>
+      </c>
+      <c r="H290" s="2" t="inlineStr">
+        <is>
+          <t>קישורים פנימיים ללא לוכסן סופי</t>
+        </is>
+      </c>
+      <c r="I290" s="2" t="inlineStr">
+        <is>
+          <t>הקישור מכיל רווח בסוף הכתובת, והשרת מפנה לכתובת ללא הרווח. לתקן את הקישור בעמודי המקור.</t>
+        </is>
+      </c>
+      <c r="J290" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/</t>
+        </is>
+      </c>
+      <c r="K290" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/coaching-for-adhd/ ‎</t>
+        </is>
+      </c>
+      <c r="B291" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C291" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D291" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/</t>
+        </is>
+      </c>
+      <c r="E291" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F291" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G291" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/positive-side-of-adhd/</t>
+        </is>
+      </c>
+      <c r="H291" s="2" t="inlineStr">
+        <is>
+          <t>קישורים פנימיים ללא לוכסן סופי</t>
+        </is>
+      </c>
+      <c r="I291" s="2" t="inlineStr">
+        <is>
+          <t>הקישור מכיל רווח בסוף הכתובת, והשרת מפנה לכתובת ללא הרווח. לתקן את הקישור בעמודי המקור.</t>
+        </is>
+      </c>
+      <c r="J291" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/</t>
+        </is>
+      </c>
+      <c r="K291" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/nlp-drugs-and-addictions/ ‎</t>
+        </is>
+      </c>
+      <c r="B292" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C292" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D292" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/</t>
+        </is>
+      </c>
+      <c r="E292" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F292" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G292" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/nlp-treatment-in-addictive-situations/</t>
+        </is>
+      </c>
+      <c r="H292" s="2" t="inlineStr">
+        <is>
+          <t>קישורים פנימיים ללא לוכסן סופי</t>
+        </is>
+      </c>
+      <c r="I292" s="2" t="inlineStr">
+        <is>
+          <t>הקישור מכיל רווח בסוף הכתובת, והשרת מפנה לכתובת ללא הרווח. לתקן את הקישור בעמודי המקור.</t>
+        </is>
+      </c>
+      <c r="J292" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/</t>
+        </is>
+      </c>
+      <c r="K292" s="5" t="inlineStr">
         <is>
           <t>נמוכה</t>
         </is>
@@ -17673,231 +17840,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="70" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>כתובת</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>קוד בסריקה 23.09</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>קוד בבדיקה חיה 27.09</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>יעד סופי / יעד להפניה</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>קפיצות</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>קישורים נכנסים</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>עמודי מקור (עד 10)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>סוג</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>פעולה נדרשת</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>יעד מומלץ להפניית 301</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>עדיפות</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/nlp-treatment-in…ctive-situations/ ‎</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/nlp-drugs-and-addictions/</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>אחר</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>הכתובת מכילה תו כיווניות בלתי נראה (U+200E/U+200F) שנוסף לקישור או לתגית (canonical/hreflang) בעמוד המקשר. להסיר את התו מהמקור.</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/coaching-for-adhd/ ‎</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/positive-side-of-adhd/</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>אחר</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>הכתובת מכילה תו כיווניות בלתי נראה (U+200E/U+200F) שנוסף לקישור או לתגית (canonical/hreflang) בעמוד המקשר. להסיר את התו מהמקור.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/nlp-drugs-and-addictions/ ‎</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/nlp-treatment-in-addictive-situations/</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>אחר</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>הכתובת מכילה תו כיווניות בלתי נראה (U+200E/U+200F) שנוסף לקישור או לתגית (canonical/hreflang) בעמוד המקשר. להסיר את התו מהמקור.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18615,7 +18557,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18886,7 +18828,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/public/crawlability-bespirit-september-2026.xlsx
+++ b/public/crawlability-bespirit-september-2026.xlsx
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -519,7 +519,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>כתובות שבורות (404): 19 כתובות (הבולטת: https://bespirit.co.il/?page_id=356, 640 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים שגויים לתיקון בעמוד המקור (ללא הפניה): 3 כתובות (הבולטת: https://bespirit.co.il/?post_type=teachers&amp;p=1759, 2 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>הפניות שמובילות לעמוד שגיאה: 5 כתובות (הבולטת: https://bespirit.co.il/הכשרת-מטפלים-בבעיות-קשב-וריכוז/, 13 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>כתובות שבורות (404): 16 כתובות (הבולטת: https://bespirit.co.il/?page_id=356, 640 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -542,14 +542,14 @@
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>בינונית</t>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>גבוהה</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>להסיר ממפת האתר כתובת אחת שמפנה ולהשאיר את כתובת היעד בלבד (במדגם של 291 כתובות שנבדקו; ייתכנו כתובות נוספות).</t>
+          <t>הפניות שמובילות לעמוד שגיאה: 5 כתובות (הבולטת: https://bespirit.co.il/הכשרת-מטפלים-בבעיות-קשב-וריכוז/, 13 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>שרשראות הפניות: כתובת אחת (הבולטת: https://bespirit.co.il/לימודים-בתחום-האימון-והאבחון/אימון-לקשב-להפרעות-קשב-וריכו, 2 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>להסיר ממפת האתר כתובת אחת שמפנה ולהשאיר את כתובת היעד בלבד (במדגם של 291 כתובות שנבדקו; ייתכנו כתובות נוספות).</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308): 288 כתובות (הבולטת: https://bespirit.co.il/allcourses/, 642 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים עם רווח בסוף הכתובת: 3 כתובות (הבולטת: https://bespirit.co.il/nlp-treatment-in…ctive-situations/ ‎, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -587,14 +587,14 @@
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>karkur.bespirit.co.il: להסיר את הרשומה ב-DNS או להגדיר noindex.</t>
+          <t>שרשראות הפניות: כתובת אחת (הבולטת: https://bespirit.co.il/לימודים-בתחום-האימון-והאבחון/אימון-לקשב-להפרעות-קשב-וריכו…, 2 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -602,14 +602,14 @@
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>בינונית</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>old.bespirit.co.il: להסיר את הרשומה ב-DNS.</t>
+          <t>קישורים פנימיים לכתובות שמפנות (301/308): 287 כתובות (הבולטת: https://bespirit.co.il/allcourses/, 642 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -624,7 +624,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים ללא לוכסן סופי: 3 כתובות (הבולטת: https://bespirit.co.il/nlp-treatment-in…ctive-situations/ ‎, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>karkur.bespirit.co.il: להסיר את הרשומה ב-DNS או להגדיר noindex.</t>
         </is>
       </c>
     </row>
@@ -632,12 +632,27 @@
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>old.bespirit.co.il: להסיר את הרשומה ב-DNS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>לבדיקה</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
         <is>
           <t>לאשר ש-4 העמודים המוגדרים noindex אכן אמורים להישאר מחוץ לאינדקס.</t>
         </is>
@@ -654,7 +669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -893,7 +908,7 @@
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>https://bespirit.co.il/?post_type=teachers&amp;p=1759</t>
+          <t>https://bespirit.co.il/plans/הכשרת-מטפלים-בבעיות-קשב-וריכוז/</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
@@ -909,12 +924,11 @@
         <v>0</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="7" t="inlineStr">
         <is>
-          <t>https://bespirit.co.il/plans/לימודי-צמחי-מרפא-הרבליסט-קליני/
-https://bespirit.co.il/plans/נטורופתיה/</t>
+          <t>https://bespirit.co.il/courses/adhd_trainers/</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -924,10 +938,14 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>קישור 'לדף המנחה' לעמוד מנחה שנמחק. להסיר את הקישור או לשחזר את עמוד המנחה.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr"/>
+          <t>לתקן או להסיר את הקישור בעמודי המקור. יעד מוצע להפניית 301 (אומת כעמוד תקין), לאישור הלקוח. העמוד שהוסר נשא את הכותרת 'מטפלים בהפרעות קשב וריכוז (ADHD)' (ארכיון דצמבר 2024); קורס אימון ADHD קיים בכתובת היעד. לאישור.</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/courses/adhd_trainers/</t>
+        </is>
+      </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
           <t>גבוהה</t>
@@ -937,7 +955,7 @@
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>https://bespirit.co.il/?post_type=teachers&amp;p=4766</t>
+          <t>https://bespirit.co.il/תכניות-רב-שנתיות/sustainable-ecology-consultants/</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
@@ -953,12 +971,11 @@
         <v>0</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>https://bespirit.co.il/plans/transpersonal-psychotherapy/
-https://bespirit.co.il/courses/איכויות-הלב/</t>
+          <t>https://bespirit.co.il/complementary-medicine-professions/</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -968,10 +985,14 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>קישור 'לדף המנחה' לעמוד מנחה שנמחק. להסיר את הקישור או לשחזר את עמוד המנחה.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr"/>
+          <t>לתקן או להסיר את הקישור בעמודי המקור. יעד מוצע להפניית 301 (אומת כעמוד תקין), לאישור הלקוח. תכנית 'לימודי סביבה וקיימות' שהוסרה; אין תכנית מקבילה פעילה. יעד משוער: קטגוריית סביבה וקיימות. לאישור.</t>
+        </is>
+      </c>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/category/כללי/סביבה-וקיימות/</t>
+        </is>
+      </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>גבוהה</t>
@@ -981,7 +1002,7 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>https://bespirit.co.il/plans/הכשרת-מטפלים-בבעיות-קשב-וריכוז/</t>
+          <t>https://bespirit.co.il/wp-content/themes/karkur/img/ttt2.png</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
@@ -997,142 +1018,9 @@
         <v>0</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/courses/adhd_trainers/</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>כתובות שבורות (404)</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור. יעד מוצע להפניית 301 (אומת כעמוד תקין), לאישור הלקוח. העמוד שהוסר נשא את הכותרת 'מטפלים בהפרעות קשב וריכוז (ADHD)' (ארכיון דצמבר 2024); קורס אימון ADHD קיים בכתובת היעד. לאישור.</t>
-        </is>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/courses/adhd_trainers/</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>גבוהה</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/?post_type=courses&amp;p=5581</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>404</v>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr"/>
-      <c r="E8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>כתובות שבורות (404)</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>מזהה קורס שנמחק. להסיר את הקישור.</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>גבוהה</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/תכניות-רב-שנתיות/sustainable-ecology-consultants/</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>404</v>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr"/>
-      <c r="E9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/complementary-medicine-professions/</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>כתובות שבורות (404)</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור. יעד מוצע להפניית 301 (אומת כעמוד תקין), לאישור הלקוח. תכנית 'לימודי סביבה וקיימות' שהוסרה; אין תכנית מקבילה פעילה. יעד משוער: קטגוריית סביבה וקיימות. לאישור.</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/category/כללי/סביבה-וקיימות/</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>גבוהה</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/wp-content/themes/karkur/img/ttt2.png</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>404</v>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr"/>
-      <c r="E10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
         <is>
           <t>https://bespirit.co.il/plans/לימודי-צמחי-מרפא-הרבליסט-קליני/
 https://bespirit.co.il/courses/הנחיית-קבוצות/
@@ -1147,6 +1035,135 @@
 (ועוד 34)</t>
         </is>
       </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>כתובות שבורות (404)</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>לתקן או להסיר את הקישור בעמודי המקור.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/wp-content/uploads/2021/01/WhatsApp-Image-2021-01-14-at-20.56.22.jpeg</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>404</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr"/>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/relaxation-and-stability/</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>כתובות שבורות (404)</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>לתקן או להסיר את הקישור בעמודי המקור.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/wp-content/uploads/2016/05/TSDS108312-patchouli-flower.jpg</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>404</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr"/>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/שמן-פטשולי-פצולי/</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>כתובות שבורות (404)</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>לתקן או להסיר את הקישור בעמודי המקור.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/wp-content/uploads/2016/05/universe-2682017_1920.jpg</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>404</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr"/>
+      <c r="E10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/דמיון-מודרך/</t>
+        </is>
+      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>כתובות שבורות (404)</t>
@@ -1167,7 +1184,7 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>https://bespirit.co.il/wp-content/uploads/2021/01/WhatsApp-Image-2021-01-14-at-20.56.22.jpeg</t>
+          <t>https://bespirit.co.il/wp-content/uploads/2016/04/ללא-שם-1500-×-999-פיקסל-12_optimized.jpg</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
@@ -1187,7 +1204,7 @@
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>https://bespirit.co.il/relaxation-and-stability/</t>
+          <t>https://bespirit.co.il/no-mind-להמונים-מאה-מדיטציות-שכל-אחד-מכיר/</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1210,7 +1227,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>https://bespirit.co.il/wp-content/uploads/2016/05/TSDS108312-patchouli-flower.jpg</t>
+          <t>https://bespirit.co.il/wp-content/uploads/2019/12/canvas-1905722_1920.jpg</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
@@ -1230,7 +1247,7 @@
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>https://bespirit.co.il/שמן-פטשולי-פצולי/</t>
+          <t>https://bespirit.co.il/training-studies-for-adhd/</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1253,7 +1270,7 @@
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>https://bespirit.co.il/wp-content/uploads/2016/05/universe-2682017_1920.jpg</t>
+          <t>https://bespirit.co.il/wp-content/uploads/2016/04/שנת-חלום.png</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
@@ -1273,7 +1290,7 @@
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>https://bespirit.co.il/דמיון-מודרך/</t>
+          <t>https://bespirit.co.il/חלומות-נעימים/</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1296,7 +1313,7 @@
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>https://bespirit.co.il/wp-content/uploads/2016/04/ללא-שם-1500-×-999-פיקסל-12_optimized.jpg</t>
+          <t>https://bespirit.co.il/wp-content/uploads/2016/05/Ravensara.jpg</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
@@ -1316,7 +1333,7 @@
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>https://bespirit.co.il/no-mind-להמונים-מאה-מדיטציות-שכל-אחד-מכיר/</t>
+          <t>https://bespirit.co.il/שעול-וצרות-אחרות-שמן-רבנסרה-ועוד/</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1339,7 +1356,7 @@
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>https://bespirit.co.il/wp-content/uploads/2019/12/canvas-1905722_1920.jpg</t>
+          <t>https://bespirit.co.il/wp-content/uploads/2016/04/bigstock-Woman-receiving-a-foot-massage-70411981-Large-1.jpg</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
@@ -1359,7 +1376,7 @@
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>https://bespirit.co.il/training-studies-for-adhd/</t>
+          <t>https://bespirit.co.il/טיפול-ברפלקסולוגיה-בשילוב-כלים-נוספי/</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1382,7 +1399,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>https://bespirit.co.il/wp-content/uploads/2016/04/שנת-חלום.png</t>
+          <t>https://bespirit.co.il/plans/מטפלים-בכלים-השלכתיים/</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1400,11 +1417,7 @@
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/חלומות-נעימים/</t>
-        </is>
-      </c>
+      <c r="G16" s="2" t="inlineStr"/>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t>כתובות שבורות (404)</t>
@@ -1412,7 +1425,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור.</t>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה; המקור עשוי להיות תגית canonical/hreflang, קובץ סטטי או קישור חיצוני. לאתר את המקור ולתקן; אין צורך בהפניה.</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
@@ -1425,7 +1438,7 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>https://bespirit.co.il/wp-content/uploads/2016/05/Ravensara.jpg</t>
+          <t>https://bespirit.co.il/plans/sustainable-ecology-consultants/</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
@@ -1445,7 +1458,7 @@
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>https://bespirit.co.il/שעול-וצרות-אחרות-שמן-רבנסרה-ועוד/</t>
+          <t>https://bespirit.co.il/disposable/</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1455,10 +1468,14 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור.</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr"/>
+          <t>לתקן או להסיר את הקישור בעמודי המקור. יעד מוצע להפניית 301 (אומת כעמוד תקין), לאישור הלקוח. תכנית 'יועצי סביבה וקיימות' שהוסרה (ארכיון יולי 2024); אין תכנית מקבילה פעילה. יעד משוער: קטגוריית סביבה וקיימות. לאישור.</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/category/כללי/סביבה-וקיימות/</t>
+        </is>
+      </c>
       <c r="K17" s="5" t="inlineStr">
         <is>
           <t>נמוכה</t>
@@ -1468,158 +1485,29 @@
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>https://bespirit.co.il/wp-content/uploads/2016/04/bigstock-Woman-receiving-a-foot-massage-70411981-Large-1.jpg</t>
+          <t>https://bespirit.co.il/הכשרת-מטפלים-בבעיות-קשב-וריכוז/</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>404</v>
+        <v>301</v>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr"/>
+          <t>301 -&gt; 404</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/plans/הכשרת-מטפלים-בבעיות-קשב-וריכוז/</t>
+        </is>
+      </c>
       <c r="E18" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/טיפול-ברפלקסולוגיה-בשילוב-כלים-נוספי/</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>כתובות שבורות (404)</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור.</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/plans/מטפלים-בכלים-השלכתיים/</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>404</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr"/>
-      <c r="E19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>כתובות שבורות (404)</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה; המקור עשוי להיות תגית canonical/hreflang, קובץ סטטי או קישור חיצוני. לאתר את המקור ולתקן; אין צורך בהפניה.</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr"/>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/plans/sustainable-ecology-consultants/</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>404</v>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr"/>
-      <c r="E20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/disposable/</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>כתובות שבורות (404)</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור. יעד מוצע להפניית 301 (אומת כעמוד תקין), לאישור הלקוח. תכנית 'יועצי סביבה וקיימות' שהוסרה (ארכיון יולי 2024); אין תכנית מקבילה פעילה. יעד משוער: קטגוריית סביבה וקיימות. לאישור.</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/category/כללי/סביבה-וקיימות/</t>
-        </is>
-      </c>
-      <c r="K20" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/הכשרת-מטפלים-בבעיות-קשב-וריכוז/</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 404</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/plans/הכשרת-מטפלים-בבעיות-קשב-וריכוז/</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
         <is>
           <t>https://bespirit.co.il/טיפול-ברכיבה-תאור-מקרה/
 https://bespirit.co.il/positive-side-of-adhd/
@@ -1634,49 +1522,49 @@
 (ועוד 2)</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>הפניות שמובילות לעמוד שגיאה</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>ההפניה מובילה לעמוד שמחזיר 404. להגדיר יעד תקין להפניה או להסיר את הקישור.</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="3" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="3" t="inlineStr">
         <is>
           <t>גבוהה</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>https://bespirit.co.il/sustainable-ecology-consultants/</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="B19" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>301 -&gt; 404</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>https://bespirit.co.il/plans/sustainable-ecology-consultants/</t>
         </is>
       </c>
-      <c r="E22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="2" t="n">
+      <c r="E19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G22" s="7" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>https://bespirit.co.il/חמישה-דברים-שניתן-ללמוד-מסוסים/
 https://bespirit.co.il/המודל-הטיפולי-הנלמד-בבית-הספר/
@@ -1686,6 +1574,144 @@
 https://bespirit.co.il/הערכת-תוכניות-של-רכיבת-סוסים-טיפולית-ע/</t>
         </is>
       </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>הפניות שמובילות לעמוד שגיאה</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>ההפניה מובילה לעמוד שמחזיר 404. להגדיר יעד תקין להפניה או להסיר את הקישור.</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>גבוהה</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/לימודים-בתחום-הרגשי-נפשי/כתיבה-יצירתית-טיפולית/</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 404</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/?post_type=courses&amp;p=5581</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/healing-power-writing/
+https://bespirit.co.il/סיפורי-ריפוי-בעקבות-כתיבה-בקורס-כתי/</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>הפניות שמובילות לעמוד שגיאה</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>ההפניה מובילה לעמוד שמחזיר 404. להגדיר יעד תקין להפניה או להסיר את הקישור.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>גבוהה</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/הכשרת-מטפלים-מוסמכים-בכלים-השלכתיים-מ/</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 404</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/plans/מטפלים-בכלים-השלכתיים/</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/complementary-medicine-professions/</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>הפניות שמובילות לעמוד שגיאה</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>ההפניה מובילה לעמוד שמחזיר 404. להגדיר יעד תקין להפניה או להסיר את הקישור.</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>גבוהה</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/courses/כתיבה-יצירתית-טיפולית/</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 404</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/?post_type=courses&amp;p=5581</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t>הפניות שמובילות לעמוד שגיאה</t>
@@ -1698,144 +1724,6 @@
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t>גבוהה</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/לימודים-בתחום-הרגשי-נפשי/כתיבה-יצירתית-טיפולית/</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 404</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/?post_type=courses&amp;p=5581</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/healing-power-writing/
-https://bespirit.co.il/סיפורי-ריפוי-בעקבות-כתיבה-בקורס-כתי/</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>הפניות שמובילות לעמוד שגיאה</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>ההפניה מובילה לעמוד שמחזיר 404. להגדיר יעד תקין להפניה או להסיר את הקישור.</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr"/>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t>גבוהה</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/הכשרת-מטפלים-מוסמכים-בכלים-השלכתיים-מ/</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 404</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/plans/מטפלים-בכלים-השלכתיים/</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/complementary-medicine-professions/</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>הפניות שמובילות לעמוד שגיאה</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>ההפניה מובילה לעמוד שמחזיר 404. להגדיר יעד תקין להפניה או להסיר את הקישור.</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr"/>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t>גבוהה</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/courses/כתיבה-יצירתית-טיפולית/</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 404</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/?post_type=courses&amp;p=5581</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>הפניות שמובילות לעמוד שגיאה</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>ההפניה מובילה לעמוד שמחזיר 404. להגדיר יעד תקין להפניה או להסיר את הקישור.</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr"/>
-      <c r="K25" s="3" t="inlineStr">
         <is>
           <t>גבוהה</t>
         </is>
@@ -1988,7 +1876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K292"/>
+  <dimension ref="A1:K288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -17629,206 +17517,6 @@
         </is>
       </c>
       <c r="K288" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/courses/לימודים-בתחום-האימון-והאבחון-אימון-לק/</t>
-        </is>
-      </c>
-      <c r="B289" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C289" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D289" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/courses/adhd_trainers/</t>
-        </is>
-      </c>
-      <c r="E289" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F289" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G289" s="2" t="inlineStr"/>
-      <c r="H289" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308)</t>
-        </is>
-      </c>
-      <c r="I289" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
-        </is>
-      </c>
-      <c r="J289" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/courses/adhd_trainers/</t>
-        </is>
-      </c>
-      <c r="K289" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/nlp-treatment-in…ctive-situations/ ‎</t>
-        </is>
-      </c>
-      <c r="B290" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C290" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D290" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/</t>
-        </is>
-      </c>
-      <c r="E290" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F290" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G290" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/nlp-drugs-and-addictions/</t>
-        </is>
-      </c>
-      <c r="H290" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים ללא לוכסן סופי</t>
-        </is>
-      </c>
-      <c r="I290" s="2" t="inlineStr">
-        <is>
-          <t>הקישור מכיל רווח בסוף הכתובת, והשרת מפנה לכתובת ללא הרווח. לתקן את הקישור בעמודי המקור.</t>
-        </is>
-      </c>
-      <c r="J290" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/</t>
-        </is>
-      </c>
-      <c r="K290" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="291">
-      <c r="A291" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/coaching-for-adhd/ ‎</t>
-        </is>
-      </c>
-      <c r="B291" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C291" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D291" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/</t>
-        </is>
-      </c>
-      <c r="E291" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F291" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G291" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/positive-side-of-adhd/</t>
-        </is>
-      </c>
-      <c r="H291" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים ללא לוכסן סופי</t>
-        </is>
-      </c>
-      <c r="I291" s="2" t="inlineStr">
-        <is>
-          <t>הקישור מכיל רווח בסוף הכתובת, והשרת מפנה לכתובת ללא הרווח. לתקן את הקישור בעמודי המקור.</t>
-        </is>
-      </c>
-      <c r="J291" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/</t>
-        </is>
-      </c>
-      <c r="K291" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="292">
-      <c r="A292" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/nlp-drugs-and-addictions/ ‎</t>
-        </is>
-      </c>
-      <c r="B292" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C292" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 200</t>
-        </is>
-      </c>
-      <c r="D292" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/</t>
-        </is>
-      </c>
-      <c r="E292" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F292" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G292" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/nlp-treatment-in-addictive-situations/</t>
-        </is>
-      </c>
-      <c r="H292" s="2" t="inlineStr">
-        <is>
-          <t>קישורים פנימיים ללא לוכסן סופי</t>
-        </is>
-      </c>
-      <c r="I292" s="2" t="inlineStr">
-        <is>
-          <t>הקישור מכיל רווח בסוף הכתובת, והשרת מפנה לכתובת ללא הרווח. לתקן את הקישור בעמודי המקור.</t>
-        </is>
-      </c>
-      <c r="J292" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/</t>
-        </is>
-      </c>
-      <c r="K292" s="5" t="inlineStr">
         <is>
           <t>נמוכה</t>
         </is>

--- a/public/crawlability-bespirit-september-2026.xlsx
+++ b/public/crawlability-bespirit-september-2026.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>להסיר ממפת האתר כתובת אחת שמפנה ולהשאיר את כתובת היעד בלבד (במדגם של 291 כתובות שנבדקו; ייתכנו כתובות נוספות).</t>
+          <t>להסיר ממפת האתר כתובת אחת שמפנה ולהשאיר את כתובת היעד בלבד (במדגם של 250 מתוך 399 הכתובות שאינן בסריקה; ייתכנו כתובות נוספות).</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>קישורים עם רווח בסוף הכתובת: 3 כתובות (הבולטת: https://bespirit.co.il/nlp-treatment-in…ctive-situations/ ‎, קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים עם רווח בסוף הכתובת: 3 כתובות (הבולטת: https://bespirit.co.il/nlp-treatment-in…ctive-situations/ [רווח בסוף], קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
+          <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr">
@@ -2057,7 +2057,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
+          <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
       <c r="J3" s="7" t="inlineStr">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
+          <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
       <c r="J7" s="7" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
+          <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
@@ -9623,7 +9623,7 @@
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
+          <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
       <c r="J135" s="7" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="I141" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
+          <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
       <c r="J141" s="7" t="inlineStr">
@@ -10523,7 +10523,7 @@
       </c>
       <c r="I152" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
+          <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
       <c r="J152" s="7" t="inlineStr">
@@ -11263,7 +11263,7 @@
       </c>
       <c r="I166" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
+          <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
       <c r="J166" s="7" t="inlineStr">
@@ -13938,7 +13938,7 @@
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>קישור פנימי לכתובת שמפנה (301). לעדכן את הקישורים הפנימיים ישירות לכתובת היעד.</t>
+          <t>הכתובת מפנה לעמוד הבית: העמוד המקורי הוסר. לשחזר את העמוד או לעדכן את הקישור לעמוד רלוונטי; אין להשאיר קישורים שמובילים לעמוד הבית דרך הפניה.</t>
         </is>
       </c>
       <c r="J218" s="7" t="inlineStr">

--- a/public/crawlability-bespirit-september-2026.xlsx
+++ b/public/crawlability-bespirit-september-2026.xlsx
@@ -11,9 +11,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="404 ושגיאות" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="לולאות, שרשראות, 302" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="קישורים להפניות 301" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="robots, sitemap, אינדוקס" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="תת-דומיינים" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מקורות" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ללא טיפול" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="robots, sitemap, אינדוקס" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="תת-דומיינים" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="מקורות" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -519,7 +520,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>קישורים שגויים לתיקון בעמוד המקור (ללא הפניה): 3 כתובות (הבולטת: https://bespirit.co.il/?post_type=teachers&amp;p=1759, 2 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים שגויים לתיקון בעמוד המקור (ללא הפניה): 3 כתובות; הבולטת https://bespirit.co.il/?post_type=teachers&amp;p=1759 (2 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -534,7 +535,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>כתובות שבורות (404): 16 כתובות (הבולטת: https://bespirit.co.il/?page_id=356, 640 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>כתובות שבורות (404): 15 כתובות; הבולטת https://bespirit.co.il/?page_id=356 (640 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -549,7 +550,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>הפניות שמובילות לעמוד שגיאה: 5 כתובות (הבולטת: https://bespirit.co.il/הכשרת-מטפלים-בבעיות-קשב-וריכוז/, 13 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>הפניות שמובילות לעמוד שגיאה: 5 כתובות; הבולטת https://bespirit.co.il/הכשרת-מטפלים-בבעיות-קשב-וריכוז/ (13 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -579,7 +580,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>קישורים עם רווח בסוף הכתובת: 3 כתובות (הבולטת: https://bespirit.co.il/nlp-treatment-in…ctive-situations/ [רווח בסוף], קישור נכנס אחד). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים עם רווח בסוף הכתובת: 3 כתובות; הבולטת https://bespirit.co.il/nlp-treatment-in…ctive-situations/ [רווח בסוף] (קישור נכנס אחד).</t>
         </is>
       </c>
     </row>
@@ -594,7 +595,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>שרשראות הפניות: כתובת אחת (הבולטת: https://bespirit.co.il/לימודים-בתחום-האימון-והאבחון/אימון-לקשב-להפרעות-קשב-וריכו…, 2 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>שרשראות הפניות: כתובת אחת; הבולטת https://bespirit.co.il/לימודים-בתחום-האימון-והאבחון/אימון-לקשב-להפרעות-קשב-וריכו… (2 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -609,7 +610,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>קישורים פנימיים לכתובות שמפנות (301/308): 287 כתובות (הבולטת: https://bespirit.co.il/allcourses/, 642 קישורים נכנסים). ראו פירוט בטבלה ובקובץ ה-Excel.</t>
+          <t>קישורים פנימיים לכתובות שמפנות (301/308): 287 כתובות; הבולטת https://bespirit.co.il/allcourses/ (642 קישורים נכנסים).</t>
         </is>
       </c>
     </row>
@@ -669,7 +670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -785,7 +786,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (אומת כעמוד תקין ב-27.09.2026). קישור 'מדיניות הפרטיות' בפוטר בכל עמודי האתר מצביע על מזהה עמוד שאינו קיים; עמוד מדיניות הפרטיות קיים בכתובת היעד. לעדכן את הקישור בתבנית הפוטר.</t>
+          <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (היעד אומת כעמוד תקין). קישור 'מדיניות הפרטיות' בפוטר בכל עמודי האתר מצביע על מזהה עמוד שאינו קיים; עמוד מדיניות הפרטיות קיים בכתובת היעד. לעדכן את הקישור בתבנית הפוטר.</t>
         </is>
       </c>
       <c r="J2" s="7" t="inlineStr">
@@ -842,7 +843,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (אומת כעמוד תקין ב-27.09.2026). העמוד שהוסר נשא את הכותרת 'לימודי פסיכותרפיה גופנית' (ארכיון 2020); תכנית לימודי פסיכותרפיה גופנית קיימת כיום בכתובת היעד.</t>
+          <t>לתקן או להסיר את הקישור בעמודי המקור. להגדיר הפניית 301 ליעד המצוין (היעד אומת כעמוד תקין). העמוד שהוסר נשא את הכותרת 'לימודי פסיכותרפיה גופנית' (ארכיון 2020); תכנית לימודי פסיכותרפיה גופנית קיימת כיום בכתובת היעד.</t>
         </is>
       </c>
       <c r="J3" s="7" t="inlineStr">
@@ -1399,7 +1400,7 @@
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>https://bespirit.co.il/plans/מטפלים-בכלים-השלכתיים/</t>
+          <t>https://bespirit.co.il/plans/sustainable-ecology-consultants/</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
@@ -1417,7 +1418,11 @@
       <c r="F16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/disposable/</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t>כתובות שבורות (404)</t>
@@ -1425,10 +1430,14 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה; המקור עשוי להיות תגית canonical/hreflang, קובץ סטטי או קישור חיצוני. לאתר את המקור ולתקן; אין צורך בהפניה.</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr"/>
+          <t>לתקן או להסיר את הקישור בעמודי המקור. יעד מוצע להפניית 301 (אומת כעמוד תקין), לאישור הלקוח. תכנית 'יועצי סביבה וקיימות' שהוסרה (ארכיון יולי 2024); אין תכנית מקבילה פעילה. יעד משוער: קטגוריית סביבה וקיימות. לאישור.</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/category/כללי/סביבה-וקיימות/</t>
+        </is>
+      </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
           <t>נמוכה</t>
@@ -1438,76 +1447,29 @@
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>https://bespirit.co.il/plans/sustainable-ecology-consultants/</t>
+          <t>https://bespirit.co.il/הכשרת-מטפלים-בבעיות-קשב-וריכוז/</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>404</v>
+        <v>301</v>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>404</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr"/>
+          <t>301 -&gt; 404</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/plans/הכשרת-מטפלים-בבעיות-קשב-וריכוז/</t>
+        </is>
+      </c>
       <c r="E17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/disposable/</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>כתובות שבורות (404)</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>לתקן או להסיר את הקישור בעמודי המקור. יעד מוצע להפניית 301 (אומת כעמוד תקין), לאישור הלקוח. תכנית 'יועצי סביבה וקיימות' שהוסרה (ארכיון יולי 2024); אין תכנית מקבילה פעילה. יעד משוער: קטגוריית סביבה וקיימות. לאישור.</t>
-        </is>
-      </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/category/כללי/סביבה-וקיימות/</t>
-        </is>
-      </c>
-      <c r="K17" s="5" t="inlineStr">
-        <is>
-          <t>נמוכה</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/הכשרת-מטפלים-בבעיות-קשב-וריכוז/</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 404</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/plans/הכשרת-מטפלים-בבעיות-קשב-וריכוז/</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>13</v>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>https://bespirit.co.il/טיפול-ברכיבה-תאור-מקרה/
 https://bespirit.co.il/positive-side-of-adhd/
@@ -1522,49 +1484,49 @@
 (ועוד 2)</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>הפניות שמובילות לעמוד שגיאה</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>ההפניה מובילה לעמוד שמחזיר 404. להגדיר יעד תקין להפניה או להסיר את הקישור.</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr"/>
-      <c r="K18" s="3" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="3" t="inlineStr">
         <is>
           <t>גבוהה</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>https://bespirit.co.il/sustainable-ecology-consultants/</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="B18" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>301 -&gt; 404</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>https://bespirit.co.il/plans/sustainable-ecology-consultants/</t>
         </is>
       </c>
-      <c r="E19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="2" t="n">
+      <c r="E18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="G18" s="7" t="inlineStr">
         <is>
           <t>https://bespirit.co.il/חמישה-דברים-שניתן-ללמוד-מסוסים/
 https://bespirit.co.il/המודל-הטיפולי-הנלמד-בבית-הספר/
@@ -1574,6 +1536,54 @@
 https://bespirit.co.il/הערכת-תוכניות-של-רכיבת-סוסים-טיפולית-ע/</t>
         </is>
       </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>הפניות שמובילות לעמוד שגיאה</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>ההפניה מובילה לעמוד שמחזיר 404. להגדיר יעד תקין להפניה או להסיר את הקישור.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>גבוהה</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/לימודים-בתחום-הרגשי-נפשי/כתיבה-יצירתית-טיפולית/</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 404</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/?post_type=courses&amp;p=5581</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/healing-power-writing/
+https://bespirit.co.il/סיפורי-ריפוי-בעקבות-כתיבה-בקורס-כתי/</t>
+        </is>
+      </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
           <t>הפניות שמובילות לעמוד שגיאה</t>
@@ -1594,7 +1604,7 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>https://bespirit.co.il/לימודים-בתחום-הרגשי-נפשי/כתיבה-יצירתית-טיפולית/</t>
+          <t>https://bespirit.co.il/הכשרת-מטפלים-מוסמכים-בכלים-השלכתיים-מ/</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
@@ -1607,19 +1617,18 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>https://bespirit.co.il/?post_type=courses&amp;p=5581</t>
+          <t>https://bespirit.co.il/plans/מטפלים-בכלים-השלכתיים/</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>https://bespirit.co.il/healing-power-writing/
-https://bespirit.co.il/סיפורי-ריפוי-בעקבות-כתיבה-בקורס-כתי/</t>
+          <t>https://bespirit.co.il/complementary-medicine-professions/</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1642,7 +1651,7 @@
     <row r="21">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>https://bespirit.co.il/הכשרת-מטפלים-מוסמכים-בכלים-השלכתיים-מ/</t>
+          <t>https://bespirit.co.il/courses/כתיבה-יצירתית-טיפולית/</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
@@ -1655,20 +1664,16 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>https://bespirit.co.il/plans/מטפלים-בכלים-השלכתיים/</t>
+          <t>https://bespirit.co.il/?post_type=courses&amp;p=5581</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/complementary-medicine-professions/</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
       <c r="H21" s="2" t="inlineStr">
         <is>
           <t>הפניות שמובילות לעמוד שגיאה</t>
@@ -1681,49 +1686,6 @@
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="3" t="inlineStr">
-        <is>
-          <t>גבוהה</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/courses/כתיבה-יצירתית-טיפולית/</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>301</v>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>301 -&gt; 404</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>https://bespirit.co.il/?post_type=courses&amp;p=5581</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>הפניות שמובילות לעמוד שגיאה</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>ההפניה מובילה לעמוד שמחזיר 404. להגדיר יעד תקין להפניה או להסיר את הקישור.</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr"/>
-      <c r="K22" s="3" t="inlineStr">
         <is>
           <t>גבוהה</t>
         </is>
@@ -17533,6 +17495,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="55" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>כתובת</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>קוד בסריקה 23.09</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>קוד בבדיקה חיה 27.09</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>יעד סופי / יעד להפניה</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>קפיצות</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>קישורים נכנסים</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>עמודי מקור (עד 10)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>סוג</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>פעולה נדרשת</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>יעד מומלץ להפניית 301</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>עדיפות</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/courses/לימודים-בתחום-האימון-והאבחון-אימון-לק/</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>301</v>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>301 -&gt; 200</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/courses/adhd_trainers/</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>כתובות מפנות ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>לא נמצאו קישורים פנימיים לכתובת בסריקה (המקור עשוי להיות canonical, hreflang, מפת האתר או קישור חיצוני). אין פעולה בקישורים; אם יאותר מקור, לעדכן אותו לכתובת היעד.</t>
+        </is>
+      </c>
+      <c r="J2" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/courses/adhd_trainers/</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>https://bespirit.co.il/plans/מטפלים-בכלים-השלכתיים/</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>404</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>כתובות 404 ללא קישור פנימי שאותר</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>לא אותר קישור פנימי לכתובת; לאתר את המקור (canonical, hreflang, קובץ סטטי או קישור חיצוני) ולתקן. אין צורך בהפניה.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -18245,7 +18377,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -18516,7 +18648,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/public/crawlability-bespirit-september-2026.xlsx
+++ b/public/crawlability-bespirit-september-2026.xlsx
@@ -476,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -632,7 +632,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>karkur.bespirit.co.il: להסיר את הרשומה ב-DNS או להגדיר noindex.</t>
+          <t>להסיר ממפת האתר כתובות של דומיין אחר (landings.bespirit.co.il) או להגישן מהדומיין שלהן.</t>
         </is>
       </c>
     </row>
@@ -646,6 +646,21 @@
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>karkur.bespirit.co.il: להסיר את הרשומה ב-DNS או להגדיר noindex.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>נמוכה</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
         <is>
           <t>old.bespirit.co.il: עמוד ברירת מחדל של שרת. להסיר את הרשומה ב-DNS או להגדיר noindex.</t>
         </is>
